--- a/models/holdings/TMC_Valuation.xlsx
+++ b/models/holdings/TMC_Valuation.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="54">
   <si>
     <t xml:space="preserve">TMC the metals company (TMC): valuation summary</t>
   </si>
@@ -81,30 +81,6 @@
   </si>
   <si>
     <t xml:space="preserve">Sell it all on a permit denial or a ruling that blocks US seabed mining. Keep it under 2% of the portfolio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Levels follow the rules on the positions page and are reset when the model changes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base value is what the business is worth if the base case plays out and you want to earn the discount rate. Implied return is what the base case earns at today's price.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCF: five explicit years, then five years fading growth, margin and reinvestment to terminal levels. FCF = operating income x (1 - tax) - net reinvestment - working capital x revenue change. Mid-year discounting from October 2026.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Margins are after stock-based pay. For ServiceNow that is about 19% today, not the 31.5% non-GAAP figure, which is the main reason its value is lower than a multiple of adjusted earnings suggests.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banks: tangible book plus the present value of returns above the cost of equity (residual income). TMC: probability-weighted, from the company's 2025 study with analyst haircuts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discount rates use a 5.31% risk-free rate and a 5% equity risk premium, the same as the earlier journal models. At these rates most quality stocks look fully priced; the implied return column shows by how much.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price and data dates are on the model sheet. Company data: Stock Analysis, company filings and releases. Research for my own records, not investment advice.</t>
   </si>
   <si>
     <t xml:space="preserve">TMC the metals company (TMC): probability-weighted scenario value</t>
@@ -344,16 +320,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -361,43 +341,43 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -405,23 +385,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -680,169 +660,141 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <f aca="false">TMC!B4</f>
         <v>2.43</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <f aca="false">TMC!B9</f>
         <v>0.15</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="5" t="n">
         <f aca="false">TMC!B19</f>
         <v>0.194476366568042</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="5" t="n">
         <f aca="false">TMC!B20</f>
         <v>2.21373781382538</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="5" t="n">
         <f aca="false">TMC!B21</f>
         <v>7.91396093257719</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="7" t="n">
         <f aca="false">F5/C5-1</f>
         <v>-0.0889967844340017</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="8" t="n">
+      <c r="J5" s="9" t="n">
         <f aca="false">IF(F5&lt;10,ROUND(F5*4,0)/4,IF(F5&lt;100,ROUND(F5,0),ROUND(F5/5,0)*5))</f>
         <v>2.25</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="8" t="n">
+      <c r="C9" s="9" t="n">
         <v>2.25</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="8" t="n">
+      <c r="C10" s="9" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="8" t="n">
+      <c r="C11" s="9" t="n">
         <v>1.5</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>27</v>
-      </c>
-    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -862,286 +814,286 @@
   <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="11" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="12" t="n">
+        <v>0.44114</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>0.09866</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>5.508</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="B8" s="13" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="10" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="C4" s="2" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="B9" s="14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="11" t="n">
+    </row>
+    <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="12" t="n">
         <v>0.44114</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="11" t="n">
-        <v>0.09866</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="12" t="n">
-        <v>5.508</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="12" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="13" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="H11" s="14" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>0.44114</v>
-      </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="8" t="n">
+      <c r="G12" s="9" t="n">
         <f aca="false">($B$7*C12+$B$8*D12+$B$6)/E12/(1+$B$9)^F12</f>
         <v>0.194476366568042</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="9" t="n">
         <f aca="false">B12*G12</f>
         <v>0.0777905466272169</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="13" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="14" t="n">
         <v>0.45</v>
       </c>
-      <c r="C13" s="15" t="n">
+      <c r="C13" s="16" t="n">
         <v>0.4</v>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="16" t="n">
         <v>0.05</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="G13" s="8" t="n">
+      <c r="G13" s="9" t="n">
         <f aca="false">($B$7*C13+$B$8*D13+$B$6)/E13/(1+$B$9)^F13</f>
         <v>2.10856250513685</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="9" t="n">
         <f aca="false">B13*G13</f>
         <v>0.948853127311581</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="13" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="14" t="n">
         <v>0.15</v>
       </c>
-      <c r="C14" s="15" t="n">
+      <c r="C14" s="16" t="n">
         <v>0.75</v>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="16" t="n">
         <v>0.2</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="12" t="n">
         <v>0.75</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="G14" s="8" t="n">
+      <c r="G14" s="9" t="n">
         <f aca="false">($B$7*C14+$B$8*D14+$B$6)/E14/(1+$B$9)^F14</f>
         <v>7.91396093257719</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="9" t="n">
         <f aca="false">B14*G14</f>
         <v>1.18709413988658</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" s="7" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="8" t="n">
         <f aca="false">SUM(B12:B14)</f>
         <v>1</v>
       </c>
-      <c r="H15" s="17" t="n">
+      <c r="H15" s="18" t="n">
         <f aca="false">SUM(H12:H14)</f>
         <v>2.21373781382538</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="B16" s="0" t="str">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="1" t="str">
         <f aca="false">IF(ABS(B15-1)&lt;0.0001,"OK","Probabilities must sum to 100%")</f>
         <v>OK</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="8" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="9" t="n">
         <f aca="false">G12</f>
         <v>0.194476366568042</v>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C19" s="7" t="n">
         <f aca="false">B19/$B$4-1</f>
         <v>-0.919968573428789</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="B20" s="8" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="9" t="n">
         <f aca="false">H15</f>
         <v>2.21373781382538</v>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C20" s="7" t="n">
         <f aca="false">B20/$B$4-1</f>
         <v>-0.0889967844340017</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="B21" s="8" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="9" t="n">
         <f aca="false">G14</f>
         <v>7.91396093257719</v>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C21" s="7" t="n">
         <f aca="false">B21/$B$4-1</f>
         <v>2.25677404632806</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B23" s="7" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="8" t="n">
         <f aca="false">(B4-G12)/((B13*G13+B14*G14)/(B13+B14)-G12)</f>
         <v>0.664259787597598</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>61</v>
+      <c r="C23" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
